--- a/backend/storage/imports/Master_SBM/3. SATUAN BIAYA TRANSPOR KEGIATAN DALAM KABUPATENKOTA PERGI PULANG (PP).xlsx
+++ b/backend/storage/imports/Master_SBM/3. SATUAN BIAYA TRANSPOR KEGIATAN DALAM KABUPATENKOTA PERGI PULANG (PP).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB10ED1-C32F-470B-8B88-676C68B0E260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFFAC7A-65C9-4442-96DB-22153FF15BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{179BC080-3BE9-4247-834C-5F925F9A9929}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>NO</t>
   </si>
@@ -98,7 +98,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,11 +121,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +150,12 @@
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EC8A25F-68D0-47F0-B57C-8317E8DD543B}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -465,45 +480,53 @@
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="1:4" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6">
         <v>3</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>-1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B3" s="2">
         <v>-2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C3" s="2">
         <v>-3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="2">
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="4" spans="1:4" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D4" s="5">
         <v>170000</v>
       </c>
     </row>
